--- a/testNinzaCRM/src/test/resources/m13.xlsx
+++ b/testNinzaCRM/src/test/resources/m13.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1BA7072E-D039-493C-AAF2-8D08AC857FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C75B4140-C8C7-4308-922B-EA66F377A1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,7 +14,7 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L9"/>
+  <oleSize ref="A1:K18"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/testNinzaCRM/src/test/resources/m13.xlsx
+++ b/testNinzaCRM/src/test/resources/m13.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C75B4140-C8C7-4308-922B-EA66F377A1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C3368D73-EE32-4E3B-9F48-7F777AB0F6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
